--- a/tame_output/ON/bt/strategyON_20240219.xlsx
+++ b/tame_output/ON/bt/strategyON_20240219.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-4.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>98.1%</t>
+          <t>98.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>1.570096507983662</v>
+        <v>1.570668874067932</v>
       </c>
       <c r="E1878" t="n">
-        <v>3.765108714813393</v>
+        <v>3.7653376612471</v>
       </c>
       <c r="F1878" t="n">
-        <v>2.30275193197498</v>
+        <v>2.303200263301296</v>
       </c>
       <c r="G1878" t="n">
-        <v>4.519077695118662</v>
+        <v>4.519346693914453</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240219.xlsx
+++ b/tame_output/ON/bt/strategyON_20240219.xlsx
@@ -43681,7 +43681,7 @@
         <v>45294</v>
       </c>
       <c r="B1832" t="n">
-        <v>3.301413393085798</v>
+        <v>3.301413393085797</v>
       </c>
       <c r="C1832" t="n">
         <v>3.130069279090508</v>
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>1.570668874067932</v>
+        <v>1.570661803337649</v>
       </c>
       <c r="E1878" t="n">
-        <v>3.7653376612471</v>
+        <v>3.765334832954987</v>
       </c>
       <c r="F1878" t="n">
-        <v>2.303200263301296</v>
+        <v>2.302912259789436</v>
       </c>
       <c r="G1878" t="n">
-        <v>4.519346693914453</v>
+        <v>4.519173891807337</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240219.xlsx
+++ b/tame_output/ON/bt/strategyON_20240219.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>450.7%</t>
+          <t>450.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-5.7%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>98.2%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>93.6%</t>
+          <t>93.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.8%</t>
+          <t>-18.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>-0.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>128.9%</t>
+          <t>127.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>123.0%</t>
+          <t>121.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.7%</t>
+          <t>-14.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>1.8%</t>
         </is>
       </c>
     </row>
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>1.570661803337649</v>
+        <v>1.558889331579601</v>
       </c>
       <c r="E1878" t="n">
-        <v>3.765334832954987</v>
+        <v>3.760625844251768</v>
       </c>
       <c r="F1878" t="n">
-        <v>2.302912259789436</v>
+        <v>2.234711082415268</v>
       </c>
       <c r="G1878" t="n">
-        <v>4.519173891807337</v>
+        <v>4.478253185382836</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240219.xlsx
+++ b/tame_output/ON/bt/strategyON_20240219.xlsx
@@ -43704,7 +43704,7 @@
         <v>45295</v>
       </c>
       <c r="B1833" t="n">
-        <v>3.311607601705545</v>
+        <v>3.311607601705544</v>
       </c>
       <c r="C1833" t="n">
         <v>3.12694133299222</v>
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045693</v>
+        <v>3.317575502045692</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -43750,7 +43750,7 @@
         <v>45297</v>
       </c>
       <c r="B1835" t="n">
-        <v>3.320996253831154</v>
+        <v>3.320996253831153</v>
       </c>
       <c r="C1835" t="n">
         <v>3.138175778137954</v>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355689</v>
+        <v>3.311888301355688</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279814</v>
+        <v>3.385382209279813</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511406</v>
+        <v>3.367379938511405</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386095</v>
+        <v>3.376932391386094</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998563</v>
+        <v>3.367370539998562</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082127</v>
+        <v>3.299560092082126</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757924</v>
+        <v>3.293490533757923</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760742</v>
+        <v>3.293766719760741</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706671</v>
+        <v>3.29873059070667</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296837</v>
+        <v>3.299918119296836</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201488</v>
+        <v>3.295507330201487</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.27276013138219</v>
+        <v>3.272760131382189</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074621</v>
+        <v>3.25147557607462</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911638</v>
+        <v>3.233800325911637</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416044</v>
+        <v>3.231167537416043</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.235981977382327</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347057</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.28737757613002</v>
+        <v>3.287377576130019</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178247</v>
+        <v>3.315884374178245</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207816</v>
+        <v>3.305316798207815</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310985</v>
+        <v>3.284619513310984</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006537</v>
+        <v>3.305849539006535</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309428</v>
+        <v>3.311086391309426</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970909</v>
+        <v>3.304715716970907</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330526</v>
+        <v>3.300815818330524</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191742</v>
+        <v>3.30261819419174</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108644</v>
+        <v>3.305023265108642</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097825</v>
+        <v>3.341378723097824</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094121</v>
+        <v>3.374439043094119</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199291</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969599</v>
+        <v>3.424633354969598</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923092</v>
+        <v>3.419979433923091</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297754</v>
+        <v>3.458100091297753</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131762</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737173</v>
+        <v>3.503515506737172</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50044609677668</v>
+        <v>3.500446096776679</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407492</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.364115398597558</v>
+        <v>3.364115398597559</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
